--- a/data/trans_orig/P0902-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67162</t>
+          <t>67667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87657</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105518</t>
+          <t>106113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146654</t>
+          <t>145702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>626850</t>
+          <t>626345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>653828</t>
+          <t>654613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600694</t>
+          <t>598190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>632021</t>
+          <t>631214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1235709</t>
+          <t>1236661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1276845</t>
+          <t>1276250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63026</t>
+          <t>63248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97367</t>
+          <t>98109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111302</t>
+          <t>112047</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152752</t>
+          <t>156901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181695</t>
+          <t>183625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237708</t>
+          <t>240038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>864433</t>
+          <t>863691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>898774</t>
+          <t>898552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>815641</t>
+          <t>811492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>857091</t>
+          <t>856346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1692485</t>
+          <t>1690155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1748498</t>
+          <t>1746568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>75297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97616</t>
+          <t>96326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135785</t>
+          <t>135994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150738</t>
+          <t>149259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198983</t>
+          <t>198927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602215</t>
+          <t>603212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633297</t>
+          <t>631928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>548056</t>
+          <t>547847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>586225</t>
+          <t>587515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1163367</t>
+          <t>1163423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1211612</t>
+          <t>1213091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60121</t>
+          <t>61853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93184</t>
+          <t>93887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154670</t>
+          <t>151499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203552</t>
+          <t>203084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220348</t>
+          <t>224388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280389</t>
+          <t>282037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849038</t>
+          <t>848335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882101</t>
+          <t>880369</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>835060</t>
+          <t>835528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>883942</t>
+          <t>887113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1700445</t>
+          <t>1698797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1760486</t>
+          <t>1756446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>238988</t>
+          <t>238484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>302230</t>
+          <t>303784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>451936</t>
+          <t>452227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>535285</t>
+          <t>533460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>713886</t>
+          <t>711231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>816233</t>
+          <t>815883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2974313</t>
+          <t>2972759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3037555</t>
+          <t>3038059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2843912</t>
+          <t>2845737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2927261</t>
+          <t>2926970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5839508</t>
+          <t>5839858</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5941855</t>
+          <t>5944510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67588</t>
+          <t>69057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102663</t>
+          <t>104763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125377</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167445</t>
+          <t>168388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203730</t>
+          <t>204677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262814</t>
+          <t>261477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>600806</t>
+          <t>598706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>635881</t>
+          <t>634412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>529605</t>
+          <t>528662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571673</t>
+          <t>574167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1137705</t>
+          <t>1139042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1196789</t>
+          <t>1195842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101460</t>
+          <t>101218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145200</t>
+          <t>143052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200200</t>
+          <t>201906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255156</t>
+          <t>257420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313692</t>
+          <t>314211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383264</t>
+          <t>382911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>871827</t>
+          <t>873975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>915567</t>
+          <t>915809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>775964</t>
+          <t>773700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>830920</t>
+          <t>829214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1664882</t>
+          <t>1665235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1734454</t>
+          <t>1733935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>50514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85171</t>
+          <t>86000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114323</t>
+          <t>115156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156813</t>
+          <t>158392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173843</t>
+          <t>174589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229530</t>
+          <t>231208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672452</t>
+          <t>671623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>707154</t>
+          <t>707109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>618449</t>
+          <t>616870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660939</t>
+          <t>660106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303355</t>
+          <t>1301677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1359042</t>
+          <t>1358296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85671</t>
+          <t>85772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128485</t>
+          <t>126712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175056</t>
+          <t>175725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227697</t>
+          <t>229037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273032</t>
+          <t>273442</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336543</t>
+          <t>339116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>819254</t>
+          <t>821027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862068</t>
+          <t>861967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>823235</t>
+          <t>821895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>875876</t>
+          <t>875207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1662129</t>
+          <t>1659556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1725640</t>
+          <t>1725230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>341647</t>
+          <t>338801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>417602</t>
+          <t>417786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>665859</t>
+          <t>662615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>756351</t>
+          <t>760522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1019635</t>
+          <t>1031353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1146997</t>
+          <t>1146398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3008256</t>
+          <t>3008072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3084211</t>
+          <t>3087057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2798012</t>
+          <t>2793841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2888504</t>
+          <t>2891748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5833225</t>
+          <t>5833824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5960587</t>
+          <t>5948869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>61081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96648</t>
+          <t>94755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129611</t>
+          <t>128406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173577</t>
+          <t>171943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203512</t>
+          <t>203657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256849</t>
+          <t>260219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>578152</t>
+          <t>580045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>612806</t>
+          <t>613719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>499262</t>
+          <t>500896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>543228</t>
+          <t>544433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1090790</t>
+          <t>1087420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1144127</t>
+          <t>1143982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76941</t>
+          <t>76029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111938</t>
+          <t>112139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148076</t>
+          <t>147532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201742</t>
+          <t>200621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>234864</t>
+          <t>234936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>299154</t>
+          <t>299486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>910493</t>
+          <t>910292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>945490</t>
+          <t>946402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>841171</t>
+          <t>842292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>894837</t>
+          <t>895381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1766190</t>
+          <t>1765858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1830480</t>
+          <t>1830408</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41766</t>
+          <t>41628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72119</t>
+          <t>71482</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107018</t>
+          <t>106797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150017</t>
+          <t>149362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158018</t>
+          <t>157153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209970</t>
+          <t>211835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>687433</t>
+          <t>688070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>717786</t>
+          <t>717924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634994</t>
+          <t>635649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>677993</t>
+          <t>678214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1334593</t>
+          <t>1332728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1386545</t>
+          <t>1387410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71687</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108958</t>
+          <t>109510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151163</t>
+          <t>149940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204464</t>
+          <t>203338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236543</t>
+          <t>232525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>299042</t>
+          <t>297930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>828609</t>
+          <t>828057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>865880</t>
+          <t>864981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>839315</t>
+          <t>840441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>892616</t>
+          <t>893839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1682304</t>
+          <t>1683416</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1744803</t>
+          <t>1748821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281101</t>
+          <t>283906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>349067</t>
+          <t>351962</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>584959</t>
+          <t>582595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>680069</t>
+          <t>673586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>884783</t>
+          <t>884720</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1002133</t>
+          <t>1001150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3045283</t>
+          <t>3042388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3113249</t>
+          <t>3110444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2864473</t>
+          <t>2870956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2959583</t>
+          <t>2961947</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5936759</t>
+          <t>5937742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6054109</t>
+          <t>6054172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73620</t>
+          <t>73915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107548</t>
+          <t>107652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114522</t>
+          <t>115093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144998</t>
+          <t>145884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197316</t>
+          <t>196972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245857</t>
+          <t>245174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>527390</t>
+          <t>527286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>561318</t>
+          <t>561023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>530214</t>
+          <t>529328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560690</t>
+          <t>560119</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1064293</t>
+          <t>1064976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1112834</t>
+          <t>1113178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59917</t>
+          <t>58269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143294</t>
+          <t>143704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168065</t>
+          <t>168230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206129</t>
+          <t>210011</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196705</t>
+          <t>184416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>343850</t>
+          <t>342421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1048790</t>
+          <t>1048380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1132167</t>
+          <t>1133815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>750911</t>
+          <t>747029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>788975</t>
+          <t>788810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1805274</t>
+          <t>1806703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1952419</t>
+          <t>1964708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81236</t>
+          <t>81793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118244</t>
+          <t>118209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,82 +7275,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>132098</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>62422</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>178236</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>230386</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>157397</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>274834</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>16,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>132098</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>72348</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>179040</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>230386</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>149138</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>272182</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586436</t>
+          <t>586471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623444</t>
+          <t>622887</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,82 +7388,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>83,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>801268</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>755130</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>870944</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>85,85%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>80,9%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1407660</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1363212</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1480649</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>83,22%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>801268</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>754326</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>861018</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,85%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>80,82%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1407660</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1365864</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1488908</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>85,94%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>83,38%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96092</t>
+          <t>94925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133008</t>
+          <t>133722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,82 +7618,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>215445</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>175982</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>244957</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>16,07%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>22,37%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>329832</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>290420</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>362953</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>14,38%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>215445</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>175171</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>242236</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>329832</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>287772</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>363778</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>14,25%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>792162</t>
+          <t>791448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>829078</t>
+          <t>830245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,82 +7731,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>879487</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>849975</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>918950</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>80,32%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>77,63%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>83,93%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2066</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1690270</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1657149</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1729682</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>82,03%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>85,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>879487</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>852696</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>919761</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>77,88%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>84,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2066</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1690270</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1656324</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1732330</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>81,99%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321017</t>
+          <t>311360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>460924</t>
+          <t>457551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>528351</t>
+          <t>539522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>724086</t>
+          <t>725184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>929269</t>
+          <t>943159</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1153476</t>
+          <t>1167569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2995949</t>
+          <t>2999322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3135856</t>
+          <t>3145513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2936464</t>
+          <t>2935366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3132199</t>
+          <t>3121028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5963947</t>
+          <t>5949854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6188154</t>
+          <t>6174264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0902-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39399</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67667</t>
+          <t>66031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>57178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90161</t>
+          <t>88144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106113</t>
+          <t>105209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145702</t>
+          <t>144243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>626345</t>
+          <t>627981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>654613</t>
+          <t>654983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>598190</t>
+          <t>600207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631214</t>
+          <t>631173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1236661</t>
+          <t>1238120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1276250</t>
+          <t>1277154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63248</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98109</t>
+          <t>97608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>108183</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156901</t>
+          <t>152902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>183625</t>
+          <t>184873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240038</t>
+          <t>239196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>863691</t>
+          <t>864192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>898552</t>
+          <t>898607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>811492</t>
+          <t>815491</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>856346</t>
+          <t>860210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1690155</t>
+          <t>1690997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1746568</t>
+          <t>1745320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46581</t>
+          <t>45583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75297</t>
+          <t>75278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96326</t>
+          <t>96498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135994</t>
+          <t>134180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149259</t>
+          <t>151623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198927</t>
+          <t>201774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603212</t>
+          <t>603231</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631928</t>
+          <t>632926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>547847</t>
+          <t>549661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>587515</t>
+          <t>587343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1163423</t>
+          <t>1160576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1213091</t>
+          <t>1210727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>60513</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93887</t>
+          <t>92593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151499</t>
+          <t>151987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203084</t>
+          <t>201859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224388</t>
+          <t>223919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282037</t>
+          <t>283126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848335</t>
+          <t>849629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880369</t>
+          <t>881709</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>835528</t>
+          <t>836753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>887113</t>
+          <t>886625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1698797</t>
+          <t>1697708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1756446</t>
+          <t>1756915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>238484</t>
+          <t>239433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>303784</t>
+          <t>300171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>452227</t>
+          <t>453785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>533460</t>
+          <t>535608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>711231</t>
+          <t>712708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>815883</t>
+          <t>815514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2972759</t>
+          <t>2976372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3038059</t>
+          <t>3037110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2845737</t>
+          <t>2843589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2926970</t>
+          <t>2925412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5839858</t>
+          <t>5840227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5944510</t>
+          <t>5943033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69057</t>
+          <t>67343</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104763</t>
+          <t>102510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122883</t>
+          <t>125417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168388</t>
+          <t>169112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204677</t>
+          <t>201315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261477</t>
+          <t>259211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>598706</t>
+          <t>600959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>636126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>528662</t>
+          <t>527938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>574167</t>
+          <t>571633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1139042</t>
+          <t>1141308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1195842</t>
+          <t>1199204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101218</t>
+          <t>100749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143052</t>
+          <t>143882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201906</t>
+          <t>203448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>257420</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>314211</t>
+          <t>315776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382911</t>
+          <t>386128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>873975</t>
+          <t>873145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>915809</t>
+          <t>916278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>773700</t>
+          <t>773639</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>829214</t>
+          <t>827672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1665235</t>
+          <t>1662018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1733935</t>
+          <t>1732370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50514</t>
+          <t>50971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86000</t>
+          <t>85471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115156</t>
+          <t>115183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158392</t>
+          <t>156157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174589</t>
+          <t>175556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231208</t>
+          <t>228158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671623</t>
+          <t>672152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>707109</t>
+          <t>706652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616870</t>
+          <t>619105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660106</t>
+          <t>660079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1301677</t>
+          <t>1304727</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1358296</t>
+          <t>1357329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85772</t>
+          <t>86974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126712</t>
+          <t>126726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175725</t>
+          <t>174635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229037</t>
+          <t>225699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273442</t>
+          <t>272644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339116</t>
+          <t>340846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821027</t>
+          <t>821013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>861967</t>
+          <t>860765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>821895</t>
+          <t>825233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>875207</t>
+          <t>876297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1659556</t>
+          <t>1657826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1725230</t>
+          <t>1726028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>338801</t>
+          <t>338802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>417786</t>
+          <t>417195</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662615</t>
+          <t>659330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>760522</t>
+          <t>755598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1025490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1146398</t>
+          <t>1146875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3008072</t>
+          <t>3008663</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3087057</t>
+          <t>3087056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2793841</t>
+          <t>2798765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2891748</t>
+          <t>2895033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5833824</t>
+          <t>5833347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5948869</t>
+          <t>5954732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61081</t>
+          <t>60694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94755</t>
+          <t>93837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128406</t>
+          <t>127384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171943</t>
+          <t>171638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203657</t>
+          <t>200503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260219</t>
+          <t>256969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>580045</t>
+          <t>580963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>613719</t>
+          <t>614106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>500896</t>
+          <t>501201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>544433</t>
+          <t>545455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1087420</t>
+          <t>1090670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1143982</t>
+          <t>1147136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76029</t>
+          <t>75984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112139</t>
+          <t>116453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147532</t>
+          <t>147286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200621</t>
+          <t>197488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>234936</t>
+          <t>234782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>299486</t>
+          <t>297075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>910292</t>
+          <t>905978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>946402</t>
+          <t>946447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>842292</t>
+          <t>845425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>895381</t>
+          <t>895627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1765858</t>
+          <t>1768269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1830408</t>
+          <t>1830562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71482</t>
+          <t>72077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106797</t>
+          <t>107575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149362</t>
+          <t>150047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157153</t>
+          <t>157317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211835</t>
+          <t>208378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>688070</t>
+          <t>687475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>717924</t>
+          <t>717616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635649</t>
+          <t>634964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>678214</t>
+          <t>677436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1332728</t>
+          <t>1336185</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387410</t>
+          <t>1387246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72586</t>
+          <t>74253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109510</t>
+          <t>110325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149940</t>
+          <t>151054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203338</t>
+          <t>204351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>232525</t>
+          <t>235268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>297930</t>
+          <t>300073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>828057</t>
+          <t>827242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>864981</t>
+          <t>863314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>840441</t>
+          <t>839428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>893839</t>
+          <t>892725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1683416</t>
+          <t>1681273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1748821</t>
+          <t>1746078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>283906</t>
+          <t>282523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>351962</t>
+          <t>350229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>582595</t>
+          <t>578553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673586</t>
+          <t>679771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>884720</t>
+          <t>877351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1001150</t>
+          <t>1003038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3042388</t>
+          <t>3044121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3110444</t>
+          <t>3111827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2870956</t>
+          <t>2864771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2961947</t>
+          <t>2965989</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5937742</t>
+          <t>5935854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6054172</t>
+          <t>6061541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -6569,17 +6569,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>97235</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73915</t>
+          <t>79115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107652</t>
+          <t>114455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>129963</t>
+          <t>139934</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115093</t>
+          <t>125876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145884</t>
+          <t>158404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>219408</t>
+          <t>237169</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196972</t>
+          <t>212232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245174</t>
+          <t>264711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -6682,17 +6682,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>545493</t>
+          <t>592982</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>527286</t>
+          <t>575762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>561023</t>
+          <t>611102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>545249</t>
+          <t>592600</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>529328</t>
+          <t>574130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560119</t>
+          <t>606658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1090742</t>
+          <t>1185582</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1064976</t>
+          <t>1158040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1113178</t>
+          <t>1210519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>690217</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>690217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>690217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675212</t>
+          <t>732534</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675212</t>
+          <t>732534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675212</t>
+          <t>732534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310150</t>
+          <t>1422751</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310150</t>
+          <t>1422751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310150</t>
+          <t>1422751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107385</t>
+          <t>116869</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58269</t>
+          <t>98094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143704</t>
+          <t>138204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>186022</t>
+          <t>209143</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168230</t>
+          <t>188488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210011</t>
+          <t>230998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>293407</t>
+          <t>326012</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>184416</t>
+          <t>298495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342421</t>
+          <t>359931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1084699</t>
+          <t>931045</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1048380</t>
+          <t>909710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1133815</t>
+          <t>949820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>771018</t>
+          <t>860585</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>747029</t>
+          <t>838730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>788810</t>
+          <t>881240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1855717</t>
+          <t>1791631</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1806703</t>
+          <t>1757712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1964708</t>
+          <t>1819148</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192084</t>
+          <t>1047914</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192084</t>
+          <t>1047914</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192084</t>
+          <t>1047914</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957040</t>
+          <t>1069728</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957040</t>
+          <t>1069728</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957040</t>
+          <t>1069728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149124</t>
+          <t>2117643</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149124</t>
+          <t>2117643</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149124</t>
+          <t>2117643</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98288</t>
+          <t>107238</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81793</t>
+          <t>89233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118209</t>
+          <t>130256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>132098</t>
+          <t>153825</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62422</t>
+          <t>136518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178236</t>
+          <t>174911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>230386</t>
+          <t>261063</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>235776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274834</t>
+          <t>291454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>606392</t>
+          <t>695835</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586471</t>
+          <t>672817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622887</t>
+          <t>713840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>801268</t>
+          <t>658434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>755130</t>
+          <t>637348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>870944</t>
+          <t>675741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1407660</t>
+          <t>1354269</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1363212</t>
+          <t>1323878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1480649</t>
+          <t>1379556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114387</t>
+          <t>118774</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94925</t>
+          <t>100167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133722</t>
+          <t>138649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>215445</t>
+          <t>231347</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175982</t>
+          <t>210050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>244957</t>
+          <t>254662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>329832</t>
+          <t>350121</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290420</t>
+          <t>320891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362953</t>
+          <t>377913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>810783</t>
+          <t>869598</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>791448</t>
+          <t>849723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830245</t>
+          <t>888205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>879487</t>
+          <t>887694</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>849975</t>
+          <t>864379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>918950</t>
+          <t>908991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1690270</t>
+          <t>1757292</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1657149</t>
+          <t>1729500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1729682</t>
+          <t>1786522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925170</t>
+          <t>988372</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925170</t>
+          <t>988372</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925170</t>
+          <t>988372</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2020102</t>
+          <t>2107413</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2020102</t>
+          <t>2107413</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2020102</t>
+          <t>2107413</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>311360</t>
+          <t>402461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>457551</t>
+          <t>481057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>663528</t>
+          <t>734249</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>539522</t>
+          <t>694929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>725184</t>
+          <t>774617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1073033</t>
+          <t>1174366</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>943159</t>
+          <t>1116300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1167569</t>
+          <t>1233820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3047368</t>
+          <t>3089460</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2999322</t>
+          <t>3048519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3145513</t>
+          <t>3127115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2997022</t>
+          <t>2999314</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2935366</t>
+          <t>2958946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3121028</t>
+          <t>3038634</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6044390</t>
+          <t>6088773</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5949854</t>
+          <t>6029319</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6174264</t>
+          <t>6146839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
